--- a/Examples/Tutorials/RunoffEtc/SoluteInRunoffCalcs.xlsx
+++ b/Examples/Tutorials/RunoffEtc/SoluteInRunoffCalcs.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aaUnderVC\ApsimX\Examples\Tutorials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\aaUnderVC\ApsimX\Examples\Tutorials\RunoffEtc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D89FDB-2B9F-4A40-99DF-A0B914807A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9088519C-1F28-4585-81B6-FB9FA4CE5989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22650" yWindow="975" windowWidth="24495" windowHeight="19635" xr2:uid="{457C1435-C66A-40C7-B0EF-CBB12B028E2E}"/>
+    <workbookView xWindow="1680" yWindow="750" windowWidth="26925" windowHeight="19470" xr2:uid="{457C1435-C66A-40C7-B0EF-CBB12B028E2E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
